--- a/data_extactor/batch_10_fa/batch_0059_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0059_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده مشتریان | Facebook | سیستم‌های اطلاعات جغرافیایی GIS | Google Android | نرم‌افزار موجودی مواد | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | نرم‌افزار محاسبه نرخ | نرم‌افزار تبدیل واحد</t>
+          <t>نرم‌افزار پایگاه داده مشتریان | Facebook | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google Android | نرم‌افزار موجودی مواد | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | نرم‌افزار محاسبه نرخ | نرم‌افزار تبدیل واحد</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب خوانده‌شده</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زیست‌شناسی | تولید و فرآوری | زبان انگلیسی | مدیریت و سازماندهی | امنیت و ایمنی عمومی | آموزش و پرورش | قانون و دولت | ریاضیات | حمل‌ونقل | شیمی | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | تولید و فرآوری | زبان انگلیسی | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | قانون و دولت | ریاضیات | حمل و نقل | شیمی | مکانیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | زبردستی دستی | بیان شفاهی | درک کتبی | وضوح گفتار | درک عمق | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
+          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | مهارت دستی | بیان شفاهی | درک کتبی | وضوح گفتار | درک عمق | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | دفعات تصمیم‌گیری | در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | فشار زمانی | در معرض شرایط خطرناک | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | ارتباط با دیگران | در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض تجهیزات خطرناک</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | اپراتورهای سیستم و کارخانه شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | کارگران مزارع و کارگران ساده، محصولات زراعی، نهالستان و گلخانه | کارگران حذف مواد خطرناک | کارگران محوطه‌سازی و نگهداری فضای سبز | کارگران خشک‌شویی و لباس‌شویی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئینات | کارگران کنترل آفات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری، فلز و پلاستیک | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله‌های فاضلاب | دانشمندان خاک و گیاه | هرس‌کنندگان و شاخه‌زن‌های درختان | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران حذف مواد خطرناک | کارگران فضای سبز و نگهداری محوطه | کارکنان خشک‌شویی و لباس‌شویی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | کارگران نقاشی، پوشش‌دهی و تزیین | کارگران کنترل آفات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | دانشمندان خاک و گیاه | هرس‌کنندگان و شاخه‌زن‌های درختان | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مکانیک</t>
+          <t>خدمات مشتری و شخصی | مکانیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | زبردستی دستی | هماهنگی چند عضو | زمان عکس‌العمل | حساسیت به مسئله | قدرت ایستا | انعطاف‌پذیری گسترده | ثبات دست و بازو | درک شفاهی | قدرت تنه | بینایی نزدیک | توجه انتخابی | قدرت پویا | بینایی دور | استدلال قیاسی | استقامت | تعادل کلی بدن | درک عمق | زبردستی انگشتان | تجسم فضایی | استدلال استقرایی | بیان شفاهی | جهت‌یابی فضایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | توجه شنیداری | هماهنگی کلی بدن | کنترل نرخ | وضوح گفتار | تشخیص گفتار</t>
+          <t>دقت کنترل | مهارت دستی | هماهنگی چند عضو | زمان عکس‌العمل | حساسیت به مسئله | قدرت ایستا | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | درک شفاهی | قدرت تنه | بینایی نزدیک | توجه انتخابی | قدرت پویا | بینایی دور | استدلال قیاسی | استقامت | تعادل کلی بدن | درک عمق | مهارت انگشتان | تجسم | استدلال استقرایی | بیان شفاهی | جهت‌گیری فضایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | توجه شنیداری | هماهنگی کلی بدن | کنترل نرخ | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | دفعات تصمیم‌گیری | در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای ایستادن | در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | سلامت و ایمنی سایر کارگران | پیامدهای کاری و نتایج سایر کارگران | مکالمات تلفنی | در معرض مکان‌های مرتفع | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فشار زمانی | صرف زمان برای خم شدن یا پیچاندن بدن | در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | سطح رقابت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای ایستادن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | قرار گرفتن در معرض ارتفاعات بالا | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | سطح رقابت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | کارگران ساختمانی | درخت‌اندازان | کارگران مزارع و کارگران ساده، محصولات زراعی، نهالستان و گلخانه | تکنسین‌های جنگل‌داری و حفاظت | کارگران جنگل‌داری و حفاظت | کارگران ساب‌زنی و پرداخت‌کاری، دستی | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه | اپراتورهای بالابر و وینچ | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران محوطه‌سازی و نگهداری فضای سبز | اپراتورهای تجهیزات قطع درختان | مهندسان اپراتور و سایر اپراتورهای تجهیزات ساختمانی | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | ریگرها | کارگران ساده نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی، چوب | تیزکنندگان و سوهان‌کاران ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | کارگران ساختمانی | قطع‌کنندگان درختان | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | کارگران سنگ‌زنی و پرداخت دستی | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران فضای سبز و نگهداری محوطه | اپراتورهای تجهیزات چوب‌بری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | ریگرها | کارگران فنی همه‌کاره نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب خوانده‌شده | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | مکانیک | زبان انگلیسی | خدمات مشتریان و شخصی | امنیت و ایمنی عمومی | شیمی | زیست‌شناسی</t>
+          <t>تولید مواد غذایی | مکانیک | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | شیمی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | فضای باز، زیر سرپناه | در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرها | در معرض مکان‌های مرتفع | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای حفظ یا بازیافتن تعادل | صرف زمان برای راه رفتن یا دویدن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارگران</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | فضای باز، زیر سقف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای حفظ یا بازیابی تعادل | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران محوطه‌سازی و نگهداری فضای سبز | هرس‌کنندگان و شاخه‌زن‌های درختان | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | سرپرستان خط اول کارگران محوطه‌سازی، خدمات چمن و نگهداری فضای سبز | کارگران کنترل آفات | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران تمیزکاری ساختمان، سایر | کارگران مزارع و کارگران ساده، محصولات زراعی، نهالستان و گلخانه | اپراتورهای تجهیزات کشاورزی | کارگران جنگل‌داری و حفاظت | کارگران تعمیر و نگهداری، عمومی | مهندسان اپراتور و سایر اپراتورهای تجهیزات ساختمانی | کارگران ساختمانی | کارگران نگهداری بزرگراه | کشاورزان، دامداران و سایر مدیران کشاورزی | دانشمندان خاک و گیاه | تکنسین‌های جنگل‌داری و حفاظت | متصدیان تفریحات و سرگرمی | مدیران تاسیسات | کارگران تفریحی</t>
+          <t>کارگران فضای سبز و نگهداری محوطه | هرس‌کنندگان و شاخه‌زن‌های درختان | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | کارگران کنترل آفات | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران تمیزکاری ساختمان، سایر موارد | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | اپراتورهای تجهیزات کشاورزی | کارگران جنگل و حفاظت | کارگران نگهداری و تعمیرات عمومی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | کارگران ساختمانی | کارگران نگهداری بزرگراه‌ها | کشاورزان، دامداران و سایر مدیران کشاورزی | دانشمندان خاک و گیاه | تکنسین‌های جنگل و حفاظت | متصدیان تفریح و سرگرمی | مدیران تسهیلات | کارکنان تفریحات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | درک مطلب خوانده‌شده | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ریاضیات | زبان انگلیسی | مدیریت و سازماندهی | کامپیوتر و الکترونیک | آموزش و پرورش | اقتصاد و حسابداری | امنیت و ایمنی عمومی | فروش و بازاریابی | پرسنل و منابع انسانی | اداری | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | آموزش و پرورش | اقتصاد و حسابداری | ایمنی و امنیت عمومی | فروش و بازاریابی | پرسنل و منابع انسانی | اداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده از نظر دما | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | اهمیت دقیق یا درست بودن | مجاورت فیزیکی | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارگران | موقعیت‌های تعارض | دفعات تصمیم‌گیری | صرف زمان برای ایستادن | فشار زمانی | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | آزادی در تصمیم‌گیری | در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران | سطح رقابت</t>
+          <t>تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | فشار زمانی | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | سطح رقابت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متصدیان تفریحات و سرگرمی | صندوق‌داران | سرویس‌کاران و تعمیرکنندگان ماشین‌های سکه‌ای، فروش خودکار و تفریحی | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول دستیاران، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکنندگان | سرپرستان خط اول کارگران فروش غیرخرده‌فروشی | سرپرستان خط اول کارگران پشتیبانی اداری و دفتری | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارگران فروش خرده‌فروشی | سرپرستان خط اول کارگران امنیتی | کارگران باجه قمار | مسئولان پول خرد و صندوق‌داران غرفه قمار | دیلرهای قمار | مدیران قمار | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | تحویل‌داران بانک</t>
+          <t>متصدیان تفریح و سرگرمی | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | دیلرهای قمار | مدیران قماربازی | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | تحویل‌داران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>سیستم‌های مدیریت موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت زمان حضور و غیاب | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
+          <t>سیستم‌های مدیریت موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت زمان | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب خوانده‌شده | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | مانیتورینگ | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و سازماندهی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | امنیت و ایمنی عمومی | فروش و بازاریابی | روان‌شناسی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | ایمنی و امنیت عمومی | فروش و بازاریابی | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | زبردستی انگشتان | زبردستی دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | مجاورت فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | داخل ساختمان, محیط کنترل‌شده از نظر دما | اهمیت تکرار وظایف یکسان | فشار زمانی | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | دفعات تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول دستیاران، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران محوطه‌سازی، خدمات چمن و نگهداری فضای سبز | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکنندگان | سرپرستان خط اول کارگران فروش غیرخرده‌فروشی | سرپرستان خط اول کارگران پشتیبانی اداری و دفتری | سرپرستان خط اول متصدیان مسافران | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارگران فروش خرده‌فروشی | سرپرستان خط اول کارگران امنیتی | مدیران کل و عملیاتی | متخصصان منابع انسانی | کارگران تفریحی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
+          <t>سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | متخصصان منابع انسانی | کارکنان تفریحات | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>سیستم‌های مدیریت موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت زمان حضور و غیاب | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
+          <t>سیستم‌های مدیریت موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت زمان | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب خوانده‌شده | مانیتورینگ | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | مدیریت و سازماندهی | امنیت و ایمنی عمومی | روان‌شناسی | پرسنل و منابع انسانی | آموزش و پرورش | اداری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ایمنی و امنیت عمومی | روان‌شناسی | پرسنل و منابع انسانی | آموزش و پرورش | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | داخل ساختمان، محیط کنترل‌شده از نظر دما | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | دفعات تصمیم‌گیری | ایمیل | فشار زمانی | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | مجاورت فیزیکی | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان</t>
+          <t>ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | ایمیل | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران آموزشی و مراقبتی، پیش‌دبستانی و مهدکودک | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول دستیاران، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران محوطه‌سازی، خدمات چمن و نگهداری فضای سبز | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکنندگان | سرپرستان خط اول کارگران فروش غیرخرده‌فروشی | سرپرستان خط اول کارگران پشتیبانی اداری و دفتری | سرپرستان خط اول متصدیان مسافران | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارگران فروش خرده‌فروشی | سرپرستان خط اول کارگران امنیتی | متخصصان منابع انسانی | مدیران خدمات پزشکی و بهداشتی | نمایندگان بیماران | مشاوران مسکونی | مدیران خدمات اجتماعی و جامعه</t>
+          <t>مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | متخصصان منابع انسانی | مدیران خدمات پزشکی و بهداشتی | نمایندگان بیمار | مشاوران خوابگاه و اقامتگاه | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | مانیتورینگ</t>
+          <t>راهبردهای یادگیری | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | آموزش و پرورش | روان‌شناسی | مدیریت و سازماندهی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | اصالت | روانی ایده‌ها | استقامت | قدرت تنه | هماهنگی چند عضو | زبردستی دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | بینایی دور | بینایی نزدیک | هماهنگی کلی بدن</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | اصالت | روانی ایده‌ها | استقامت | قدرت تنه | هماهنگی چند عضو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | بینایی دور | بینایی نزدیک | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | دفعات تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | فضای باز، زیر سرپناه</t>
+          <t>آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان تفریحات و سرگرمی | پرورش‌دهندگان حیوانات | مراقبان حیوانات | کارگران کنترل حیوانات | دانشمندان علوم دامی | ورزشکاران و رقابت‌کنندگان ورزشی | مربیان ورزشی | مربیان و استعداد‌یاب‌ها | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مربیان تناسب اندام گروهی | کارگران مزارع، حیوانات مزرعه، دامداری و آبزی‌پروری | نجات‌غریق‌ها، گشت اسکی و سایر کارگران خدمات حفاظتی تفریحی | معلمان خودشکوفایی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | داوران، خط‌نگهداران و سایر مقامات ورزشی | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و تکنولوژیست‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>متصدیان تفریح و سرگرمی | پرورش‌دهندگان حیوانات | مراقبان حیوانات | کارکنان کنترل حیوانات | دانشمندان علوم دامی | ورزشکاران و رقبای ورزشی | مربیان ورزشی | مربیان و استعدادیاب‌ها | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مدرسان تناسب اندام گروهی | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | معلمان خودسازی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | درک مطلب خوانده‌شده</t>
+          <t>نظارت | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | اداری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده از نظر دما | ارتباط با دیگران | در معرض صداها, سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | دفعات تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | در معرض آلاینده‌ها | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | مجاورت فیزیکی | آزادی در تصمیم‌گیری | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | در معرض بیماری یا عفونت‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرورش‌دهندگان حیوانات | کارگران کنترل حیوانات | دانشمندان علوم دامی | مربیان حیوانات | مددکاران اجتماعی کودک، خانواده و مدرسه | کارگران مراقبت از کودک | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران مزارع، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران خدمات شخصی | دستیاران سلامت در خانه | پرستاران عملیاتی مجاز و پرستاران حرفه‌ای مجاز | متصدیان رختکن، اتاق لباس و اتاق پرو | دستیاران پرستاری | دستیاران مراقبت شخصی | فلبوتومیست‌ها | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و تکنولوژیست‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>پرورش‌دهندگان حیوانات | کارکنان کنترل حیوانات | دانشمندان علوم دامی | مربیان حیوانات | مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و کارکنان مراقبت از کودکان | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران خدمات شخصی | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متصدیان رختکن، اتاق لباس و اتاق پرو | کمک‌پرستاران | کمک‌یاران مراقبت شخصی | فلبوتومیست‌ها | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب خوانده‌شده</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ریاضیات | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | زبردستی انگشتان | ترتیب‌دهی اطلاعات | استدلال قیاسی | زبردستی دستی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | مهارت انگشتان | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | داخل ساختمان، محیط کنترل‌شده از نظر دما | ارتباط با دیگران | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | مجاورت فیزیکی | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | دفعات تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سطح رقابت</t>
+          <t>اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سطح رقابت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان تفریحات و سرگرمی | ورزشکاران و رقابت‌کنندگان ورزشی | کارمندان کارگزاری | صندوق‌داران | سرویس‌کاران و تعمیرکنندگان ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کارمندان پیشخوان و اجاره | کارشناسان خدمات مشتریان | کارگران فروش خانه‌به‌خانه، فروشندگان روزنامه و خیابانی، و کارگران مرتبط | سرپرستان خط اول کارگران خدمات قمار | کارگران باجه قمار | مسئولان پول خرد و صندوق‌داران غرفه قمار | مدیران قمار | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | کارمندان حساب‌های جدید | فروشندگان خرده‌فروشی | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | تحویل‌داران بانک | داوران، خط‌نگهداران و سایر مقامات ورزشی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
+          <t>متصدیان تفریح و سرگرمی | ورزشکاران و رقبای ورزشی | کارمندان کارگزاری | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان خط اول کارگران خدمات قمار | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | مدیران قماربازی | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | کارمندان حساب‌های جدید | فروشندگان خرده‌فروشی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | مانیتورینگ | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | استدلال قیاسی | استدلال ریاضی | استدلال استقرایی | بیان کتبی | درک کتبی | سهولت کار با اعداد</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | استدلال قیاسی | استدلال ریاضی | استدلال استقرایی | بیان کتبی | درک کتبی | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده از نظر دما | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مجاورت فیزیکی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سر و کار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان تفریحات و سرگرمی | ورزشکاران و رقابت‌کنندگان ورزشی | کارمندان دفترداری، حسابداری و حسابرسی | صندوق‌داران | کارمندان پیشخوان و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | کارگران فروش خانه‌به‌خانه، فروشندگان روزنامه و خیابانی، و کارگران مرتبط | سرپرستان خط اول کارگران خدمات قمار | کارگران باجه قمار | مسئولان پول خرد و صندوق‌داران غرفه قمار | دیلرهای قمار | مدیران قمار | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و تفریحگاه | کارمندان حساب‌های جدید | فروشندگان خرده‌فروشی | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | انبارداران و پرکنندگان سفارش | تحویل‌داران بانک | داوران، خط‌نگهداران و سایر مقامات ورزشی</t>
+          <t>متصدیان تفریح و سرگرمی | ورزشکاران و رقبای ورزشی | کارمندان دفترداری، حسابداری و حسابرسی | صندوق‌داران | کارمندان باجه و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان خط اول کارگران خدمات قمار | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | دیلرهای قمار | مدیران قماربازی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان حساب‌های جدید | فروشندگان خرده‌فروشی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | قفسه‌چین‌ها و پرکننده‌های سفارش | تحویل‌داران | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0059_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0059_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زیست‌شناسی | تولید و فرآوری | زبان انگلیسی | مدیریت و امور اداری | ایمنی و امنیت عمومی | آموزش و تدریس | حقوق و مقررات دولتی | ریاضیات | حمل‌ونقل | شیمی | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | تولید و فرآوری | زبان انگلیسی | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | قانون و دولت | ریاضیات | حمل و نقل | شیمی | مکانیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | هماهنگی اندام‌ها | چابکی دستی | بیان شفاهی | درک کتبی | وضوح گفتار | درک عمق | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | مهارت دستی | بیان شفاهی | درک کتبی | وضوح گفتار | درک عمق | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | اپراتورهای کارخانه‌ها و سیستم‌های شیمیایی | پاک‌کنندگان وسایل نقلیه و تجهیزات | اپراتورهای تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | کارگران مزارع، باغات و گلخانه‌ها | کارگران امحای مواد خطرناک | کارگران باغبانی و محوطه‌سازی | کارگران لباسشویی و خشک‌شویی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات مخلوط‌کن و همزن | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | کارگران کنترل آفات و سم‌پاشی | تنظیم‌کنندگان و اپراتورهای تجهیزات آبکاری فلز و پلاستیک | اپراتورهای پمپ به‌جز پمپ‌های سرچاهی نفت | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی و تقطیر | سرویس‌کاران مخازن فاضلاب و پاک‌کنندگان لوله‌های فاضلاب | دانشمندان علوم خاک و گیاه‌شناسی | هرس‌کنندگان درختان | اپراتورهای تصفیه‌خانه و سیستم‌های آب و فاضلاب</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | کارگران زراعت، نهالستان و گلخانه | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران خشکشویی و رختشویخانه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | کارگران سم‌پاشی و دفع آفات | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | متخصصان خاک‌شناسی و علوم گیاهی | هرس‌کنندگان و پیرایندگان درختان | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Outlook | Microsoft Word | Facebook</t>
+          <t>Facebook | Microsoft Outlook | Microsoft Word | Facebook</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک</t>
+          <t>خدمات مشتری و شخصی | مکانیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | چابکی دستی | هماهنگی اندام‌ها | زمان واکنش | حساسیت به مسئله | قدرت ایستا | دامنه انعطاف‌پذیری | ثبات دست و بازو | درک شفاهی | استحکام تنه | دید نزدیک | توجه انتخابی | قدرت پویا | دید دور | استدلال قیاسی | استقامت بدنی | تعادل کلی بدن | درک عمق | چابکی انگشتان | تجسم فضایی | استدلال استقرایی | بیان شفاهی | جهت‌یابی فضایی | انعطاف‌پذیری ادراک شکل | مرتب‌سازی اطلاعات | توجه شنیداری | هماهنگی کلی بدن | کنترل سرعت حرکت | وضوح گفتار | تشخیص گفتار</t>
+          <t>دقت کنترل | مهارت دستی | هماهنگی چند عضو | زمان عکس‌العمل | حساسیت به مسئله | قدرت ایستا | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | درک شفاهی | قدرت تنه | بینایی نزدیک | توجه انتخابی | قدرت پویا | بینایی دور | استدلال قیاسی | استقامت | تعادل کلی بدن | درک عمق | مهارت انگشتان | تجسم | استدلال استقرایی | بیان شفاهی | جهت‌گیری فضایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | توجه شنیداری | هماهنگی کلی بدن | کنترل نرخ | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | کارگران ساختمانی | چوب‌بُران و درخت‌اندازان | کارگران مزارع، باغات و گلخانه‌ها | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران جنگل‌داری و حفاظت | کارگران ساب‌زنی و پرداخت‌کاری دستی | کمک‌کارگران استخراج معدن | کارگران نگهداری و تعمیرات بزرگراه‌ها | اپراتورهای بالابر و وینچ | کارگران جابه‌جایی دستی بار و کالا | کارگران باغبانی و محوطه‌سازی | اپراتورهای ماشین‌آلات چوب‌بُری و الوارسازی | اپراتورهای ماشین‌آلات عمرانی و مهندسی عملیات | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | ریگرها و قلاب‌اندازان بار | کارگران ساده صنعت نفت و گاز | تنظیم‌کنندگان و اپراتورهای اره‌کشی چوب | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | کارگران ساختمانی | درخت‌اندازان و چوب‌بُران جنگل | کارگران زراعت، نهالستان و گلخانه | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کارگران کمکی استخراج معدن | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران باغبانی، فضای سبز و نگهداری محوطه | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران عمومی سکو و میادین نفت و گاز | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | مکانیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | شیمی | زیست‌شناسی</t>
+          <t>تولید مواد غذایی | مکانیک | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | شیمی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | استحکام تنه | استقامت بدنی | دید نزدیک | دید دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | دامنه انعطاف‌پذیری | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران باغبانی و محوطه‌سازی | هرس‌کنندگان و پیرایندگان درختان | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرپرستان رده‌اول کارگران باغبانی، فضای سبز و محوطه‌سازی | کارگران کنترل آفات و سم‌پاشی | سرایداران و پاکبانان، به‌جز نظافتچیان منازل | سایر کارگران نظافت ساختمان | کارگران مزارع، باغات و گلخانه‌ها | اپراتورهای تجهیزات کشاورزی | کارگران جنگل‌داری و حفاظت | کارگران تعمیرات و نگهداری عمومی | اپراتورهای ماشین‌آلات عمرانی و مهندسی عملیات | کارگران ساختمانی | کارگران نگهداری و تعمیرات بزرگراه‌ها | مدیران مزارع، دامپروری‌ها و سایر واحدهای کشاورزی | دانشمندان علوم خاک و گیاه‌شناسی | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | متصدیان اماکن تفریحی و شهربازی‌ها | مدیران تأسیسات | کارشناسان امور تفریحی و اوقات فراغت</t>
+          <t>کارگران باغبانی، فضای سبز و نگهداری محوطه | هرس‌کنندگان و پیرایندگان درختان | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران سم‌پاشی و دفع آفات | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | سایر کارگران نظافت ساختمان | کارگران زراعت، نهالستان و گلخانه | اپراتورهای ماشین‌آلات و ادوات کشاورزی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران عمومی تعمیرات و نگهداری تاسیسات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | کارگران ساختمانی | کارگران راهداری و نگهداری جاده‌ها | مدیران امور کشاورزی، دامپروری و شیلات | متخصصان خاک‌شناسی و علوم گیاهی | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | متصدیان اماکن تفریحی و شهربازی | مدیران امور ساختمان و تأسیسات | کارکنان و متصدیان امور تفریحی و اوقات فراغت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | کامپیوتر و الکترونیک | آموزش و تدریس | اقتصاد و حسابداری | ایمنی و امنیت عمومی | فروش و بازاریابی | پرسنلی و منابع انسانی | امور دفتری و اداری | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | آموزش و پرورش | اقتصاد و حسابداری | ایمنی و امنیت عمومی | فروش و بازاریابی | پرسنل و منابع انسانی | اداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | دید نزدیک | استدلال قیاسی | بیان کتبی | درک کتبی | توجه انتخابی | مرتب‌سازی اطلاعات | دید دور | استدلال استقرایی | به‌خاطرسپاری | انعطاف‌پذیری ادراک شکل | سرعت ادراک شکل</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | استدلال قیاسی | بیان کتبی | درک کتبی | توجه انتخابی | ترتیب‌دهی اطلاعات | بینایی دور | استدلال استقرایی | حفظ کردن | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده، باربران و جابه‌جاکنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات نظافتی و خانه‌داری | سرپرستان رده‌اول اپراتورهای وسایل نقلیه و ماشین‌آلات جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | متصدیان باجه و خزانه‌داری سالن‌های بازی | متصدیان تبدیل ژتون و تحویل‌داران باجه | دیلرها و گردانندگان بازی‌های میزی | مدیران مراکز بازی و تفریحات | بازرسان و مأموران نظارت تصویری سالن‌های بازی | ثبت‌کنندگان و متصدیان شرط‌بندی‌های ورزشی | متصدیان باجه‌های بانکی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | گردانندگان بازی‌های میزی و کازینویی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | پرسنلی و منابع انسانی | آموزش و تدریس | ایمنی و امنیت عمومی | فروش و بازاریابی | روان‌شناسی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | ایمنی و امنیت عمومی | فروش و بازاریابی | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تسهیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به‌خاطرسپاری | روانی ایده‌ها | بیان کتبی | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول مشاغل ساختمانی و استخراج معدن | سرپرستان رده‌اول کارکنان کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده، باربران و جابه‌جاکنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات نظافتی و خانه‌داری | سرپرستان رده‌اول کارگران باغبانی، فضای سبز و محوطه‌سازی | سرپرستان رده‌اول اپراتورهای وسایل نقلیه و ماشین‌آلات جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران عمومی و عملیاتی | کارشناسان منابع انسانی | مربیان و کارشناسان امور تفریحی و اوقات فراغت | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | کارشناسان منابع انسانی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | ایمنی و امنیت عمومی | روان‌شناسی | پرسنلی و منابع انسانی | آموزش و تدریس | امور دفتری و اداری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ایمنی و امنیت عمومی | روان‌شناسی | پرسنل و منابع انسانی | آموزش و پرورش | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ابتکار و اصالت | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده، باربران و جابه‌جاکنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات نظافتی و خانه‌داری | سرپرستان رده‌اول کارگران باغبانی، فضای سبز و محوطه‌سازی | سرپرستان رده‌اول اپراتورهای وسایل نقلیه و ماشین‌آلات جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافری | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان منابع انسانی | مدیران خدمات بهداشتی و درمانی | نمایندگان و رابطان حقوق بیماران | مشاوران و سرپرستان خوابگاه‌ها و اقامتگاه‌ها | مدیران خدمات اجتماعی و خدمات رفاهی جامعه</t>
+          <t>مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان منابع انسانی | مدیران خدمات درمانی و بهداشتی | کارشناسان امور بیماران و پذیرش | سرپرستان و مشاوران خوابگاه | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | سخن گفتن | تفکر انتقادی | یادگیری فعال | شنیدن فعال | نظارت</t>
+          <t>راهبردهای یادگیری | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | ابتکار و اصالت | روانی ایده‌ها | استقامت بدنی | استحکام تنه | هماهنگی اندام‌ها | چابکی دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | دید دور | دید نزدیک | هماهنگی کلی بدن</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | اصالت | روانی ایده‌ها | استقامت | قدرت تنه | هماهنگی چند عضو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | بینایی دور | بینایی نزدیک | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | پرورش‌دهندگان حیوانات | مراقبان و نگهداران حیوانات | ماموران کنترل و زنده‌گیری حیوانات | دانشمندان علوم دامی | ورزشکاران و قهرمانان ورزشی | مربیان بدنسازی و آمادگی جسمانی | مربیان و استعدادیاب‌های ورزشی | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مربیان تناسب اندام گروهی | کارگران مزارع پرورش دام، طیور و آبزیان | نجات‌غریق‌ها، گشت‌های نجات و سایر کارکنان خدمات حفاظتی تفریحی | مدرسان آموزش‌های آزاد و دوره‌های کوتاه‌مدت | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی | داوران و مسئولان مسابقات ورزشی | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کاردان‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | مراقبان و نگهداران حیوانات | ماموران کنترل و ساماندهی حیوانات | متخصصان علوم دامی | ورزشکاران و قهرمانان حرفه‌ای | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مربیان و استعدادیابان ورزشی | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | کارگران پرورش دام، طیور و آبزیان | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | داوران و مسئولان مسابقات ورزشی | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور دفتری و اداری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | دید نزدیک | قدرت ایستا | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | استحکام تنه | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | قدرت ایستا | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | قدرت تنه | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرورش‌دهندگان حیوانات | ماموران کنترل و زنده‌گیری حیوانات | دانشمندان علوم دامی | مربیان و رام‌کنندگان حیوانات | مددکاران اجتماعی کودک، خانواده و مدارس | مربیان مهدکودک و مراقبان کودک | مدیران مزارع، دامپروری‌ها و سایر واحدهای کشاورزی | کارگران مزارع پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارکنان کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | بهیاران و مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | متصدیان رختکن‌ها و اتاق‌های تعویض لباس | کمک‌بهیاران | مراقبان خدمات فردی | خون‌گیران و فلبوتومیست‌ها | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کاردان‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | ماموران کنترل و ساماندهی حیوانات | متخصصان علوم دامی | مربیان و رام‌کنندگان حیوانات | مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | مدیران امور کشاورزی، دامپروری و شیلات | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | متصدیان رختکن، امانات و اتاق پرو | کمک‌پرستاران | مراقبان خدمات شخصی و همراهان توان‌خواهان | کارشناسان و تکنسین‌های خون‌گیری | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | چابکی انگشتان | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی دستی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | مهارت انگشتان | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | ورزشکاران و قهرمانان ورزشی | کارمندان کارگزاری‌های بورس | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | کارمندان پذیرش و اجاره کالا | کارشناسان خدمات و پشتیبانی مشتریان | فروشندگان دوره‌گرد، روزنامه‌فروشان و دست‌فروشان خیابانی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان باجه و خزانه‌داری سالن‌های بازی | متصدیان تبدیل ژتون و تحویل‌داران باجه | مدیران مراکز بازی و تفریحات | بازرسان و مأموران نظارت تصویری سالن‌های بازی | ثبت‌کنندگان و متصدیان شرط‌بندی‌های ورزشی | کارمندان افتتاح حساب | فروشندگان خرده‌فروشی | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | متصدیان باجه‌های بانکی | داوران و مسئولان مسابقات ورزشی | خریداران عمده و خرده‌فروشی به‌جز محصولات کشاورزی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | ورزشکاران و قهرمانان حرفه‌ای | کارشناسان امور اداری و معاملات کارگزاری | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | متصدیان افتتاح حساب | فروشندگان خرده‌فروشی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران و متصدیان امور بانکی | داوران و مسئولان مسابقات ورزشی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | دید دور | استدلال قیاسی | استدلال ریاضی | استدلال استقرایی | بیان کتبی | درک کتبی | مهارت کار با اعداد و محاسبات</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | استدلال قیاسی | استدلال ریاضی | استدلال استقرایی | بیان کتبی | درک کتبی | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | ورزشکاران و قهرمانان ورزشی | کارمندان حسابداری، دفاتر مالی و حسابرسی | صندوق‌داران | کارمندان پذیرش و اجاره کالا | کارشناسان اعتبارسنجی و تایید اعتبار مشتریان | فروشندگان دوره‌گرد، روزنامه‌فروشان و دست‌فروشان خیابانی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان باجه و خزانه‌داری سالن‌های بازی | متصدیان تبدیل ژتون و تحویل‌داران باجه | دیلرها و گردانندگان بازی‌های میزی | مدیران مراکز بازی و تفریحات | متصدیان پذیرش و میزبانی رستوران‌ها و کافی‌شاپ‌ها | کارمندان پذیرش هتل، متل و مجتمع‌های اقامتی | کارمندان افتتاح حساب | فروشندگان خرده‌فروشی | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | کارگران انبار، چیدمان و جمع‌آوری سفارش‌ها | متصدیان باجه‌های بانکی | داوران و مسئولان مسابقات ورزشی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | ورزشکاران و قهرمانان حرفه‌ای | کارمندان دفترداری، حسابداری و امور حسابرسی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | گردانندگان بازی‌های میزی و کازینویی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان افتتاح حساب | فروشندگان خرده‌فروشی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | متصدیان چیدمان و آماده‌سازی سفارش | تحویل‌داران و متصدیان امور بانکی | داوران و مسئولان مسابقات ورزشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
